--- a/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/SneakerPark_Dashboard_Metrics.xlsx
+++ b/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/SneakerPark_Dashboard_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be4ab9aaf12c5868/Documents/Github/Udacity-Master-Artificial-Intelligence/udacity-ai-masters/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36337712-9A01-435C-A951-24D38AC3CFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{36337712-9A01-435C-A951-24D38AC3CFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A98E3618-C91C-44F3-89ED-EC64B218CAAD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Data Quality Rule</t>
   </si>
@@ -53,25 +53,10 @@
     <t>Total Records</t>
   </si>
   <si>
-    <t>Calculation</t>
-  </si>
-  <si>
     <t>Data Quality Score</t>
   </si>
   <si>
     <t>Invalid Customer Email Addresses</t>
-  </si>
-  <si>
-    <t>(400-0)/400×100</t>
-  </si>
-  <si>
-    <t>(304-96)/304×100</t>
-  </si>
-  <si>
-    <t>(91-7)/91×100</t>
-  </si>
-  <si>
-    <t>(244-186)/244×100</t>
   </si>
   <si>
     <t>Rule</t>
@@ -121,7 +106,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(Total Records − Total Issues) / Total Records × 100</t>
+      <t>(Total Records − Issue Records) / Total Records × 100</t>
     </r>
   </si>
 </sst>
@@ -490,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -510,35 +495,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -592,6 +555,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -757,7 +741,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Dashboard Metrics'!$H$4</c:f>
+              <c:f>'Dashboard Metrics'!$G$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -778,7 +762,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard Metrics'!$G$5:$G$8</c:f>
+              <c:f>'Dashboard Metrics'!$F$5:$F$8</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -798,7 +782,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard Metrics'!$H$5:$H$8</c:f>
+              <c:f>'Dashboard Metrics'!$G$5:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1545,13 +1529,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>1478280</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1580,10 +1564,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1871,394 +1851,294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.77734375" customWidth="1"/>
     <col min="2" max="2" width="14.21875" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
-    <col min="8" max="8" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.21875" customWidth="1"/>
-    <col min="10" max="10" width="4.77734375" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.21875" customWidth="1"/>
+    <col min="9" max="9" width="4.77734375" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="F1" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="18"/>
+      <c r="B2" s="26">
+        <v>400</v>
+      </c>
+      <c r="C2" s="26">
+        <v>91</v>
+      </c>
+      <c r="D2" s="28">
+        <v>0.77</v>
+      </c>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="25">
+        <v>98</v>
+      </c>
+      <c r="C3" s="25">
+        <v>7</v>
+      </c>
+      <c r="D3" s="30">
+        <v>0.93</v>
+      </c>
+      <c r="F3" s="14"/>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="25">
+        <v>400</v>
+      </c>
+      <c r="C4" s="25">
+        <v>0</v>
+      </c>
+      <c r="D4" s="30">
+        <v>1</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="34">
-        <v>400</v>
-      </c>
-      <c r="C2" s="34">
-        <v>91</v>
-      </c>
-      <c r="D2" s="34" t="s">
+      <c r="G4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="38"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32">
+        <v>430</v>
+      </c>
+      <c r="C5" s="32">
+        <v>186</v>
+      </c>
+      <c r="D5" s="33">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F5" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="36">
+      <c r="G5" s="8">
+        <f>D2</f>
         <v>0.77</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="21"/>
+      <c r="H5" s="7" t="str">
+        <f>IF(G5&gt;=0.9,"✓ Excellent",IF(G5&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
+        <v>◐ Good</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="40"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="33">
-        <v>98</v>
-      </c>
-      <c r="C3" s="33">
-        <v>7</v>
-      </c>
-      <c r="D3" s="33" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="38">
+      <c r="G6" s="8">
+        <f>D3</f>
         <v>0.93</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="23"/>
+      <c r="H6" s="7" t="str">
+        <f>IF(G6&gt;=0.9,"✓ Excellent",IF(G6&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
+        <v>✓ Excellent</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="41"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="33">
-        <v>400</v>
-      </c>
-      <c r="C4" s="33">
-        <v>0</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="38">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F7" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="8">
+        <f>D4</f>
         <v>1</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="H7" s="7" t="str">
+        <f>IF(G7&gt;=0.9,"✓ Excellent",IF(G7&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
+        <v>✓ Excellent</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="42"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="1"/>
+      <c r="F8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="46"/>
+      <c r="G8" s="8">
+        <f>D5</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f>IF(G8&gt;=0.9,"✓ Excellent",IF(G8&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
+        <v>✗ Needs Attention</v>
+      </c>
+      <c r="K8" s="15"/>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="40">
-        <v>430</v>
-      </c>
-      <c r="C5" s="40">
-        <v>186</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="41">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="G5" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="10">
-        <f>E2</f>
-        <v>0.77</v>
-      </c>
-      <c r="I5" s="9" t="str">
-        <f>IF(H5&gt;=0.9,"✓ Excellent",IF(H5&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
-        <v>◐ Good</v>
-      </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="48"/>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F9" s="14"/>
+      <c r="K9" s="15"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G6" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="10">
-        <f>E3</f>
-        <v>0.93</v>
-      </c>
-      <c r="I6" s="9" t="str">
-        <f>IF(H6&gt;=0.9,"✓ Excellent",IF(H6&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
-        <v>✓ Excellent</v>
-      </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="49"/>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F10" s="17"/>
+      <c r="K10" s="15"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G7" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="10">
-        <f>E4</f>
-        <v>1</v>
-      </c>
-      <c r="I7" s="9" t="str">
-        <f>IF(H7&gt;=0.9,"✓ Excellent",IF(H7&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
-        <v>✓ Excellent</v>
-      </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="50"/>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F11" s="18"/>
+      <c r="K11" s="15"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="G8" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="10">
-        <f>E5</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="I8" s="9" t="str">
-        <f>IF(H8&gt;=0.9,"✓ Excellent",IF(H8&gt;=0.7,"◐ Good","✗ Needs Attention"))</f>
-        <v>✗ Needs Attention</v>
-      </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="23"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G9" s="22"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="23"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G10" s="25"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="23"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G11" s="26"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="23"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="4"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="23"/>
+      <c r="D12" s="4"/>
+      <c r="F12" s="19"/>
+      <c r="K12" s="15"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="23"/>
+      <c r="D13" s="6"/>
+      <c r="F13" s="20"/>
+      <c r="K13" s="15"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="23"/>
+      <c r="D14" s="6"/>
+      <c r="F14" s="14"/>
+      <c r="K14" s="15"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="23"/>
+      <c r="D15" s="6"/>
+      <c r="F15" s="14"/>
+      <c r="K15" s="15"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="23"/>
+      <c r="D16" s="6"/>
+      <c r="F16" s="14"/>
+      <c r="K16" s="15"/>
     </row>
-    <row r="17" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G17" s="22"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="23"/>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F17" s="14"/>
+      <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G18" s="22"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="23"/>
+    <row r="18" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F18" s="14"/>
+      <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G19" s="22"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="23"/>
+    <row r="19" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F19" s="14"/>
+      <c r="K19" s="15"/>
     </row>
-    <row r="20" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G20" s="22"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="23"/>
+    <row r="20" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F20" s="14"/>
+      <c r="K20" s="15"/>
     </row>
-    <row r="21" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G21" s="22"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="23"/>
+    <row r="21" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F21" s="14"/>
+      <c r="K21" s="15"/>
     </row>
-    <row r="22" spans="7:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G22" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="32"/>
-    </row>
-    <row r="23" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
+    <row r="22" spans="6:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F22" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="G1:L2"/>
+    <mergeCell ref="F1:K2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="I19:I20">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Excellent">
-      <formula>NOT(ISERROR(SEARCH("Excellent",I19)))</formula>
+  <conditionalFormatting sqref="H5:H8">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Excellent">
+      <formula>NOT(ISERROR(SEARCH("Excellent",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Attention">
+      <formula>NOT(ISERROR(SEARCH("Attention",H5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I19:I20">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",I19)))</formula>
+  <conditionalFormatting sqref="H19:H20">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Excellent">
+      <formula>NOT(ISERROR(SEARCH("Excellent",H19)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I19:I20">
-    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Attention">
-      <formula>NOT(ISERROR(SEARCH("Attention",I19)))</formula>
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Good">
+      <formula>NOT(ISERROR(SEARCH("Good",H19)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I8">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Excellent">
-      <formula>NOT(ISERROR(SEARCH("Excellent",I5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I8">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Good">
-      <formula>NOT(ISERROR(SEARCH("Good",I5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I8">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Attention">
-      <formula>NOT(ISERROR(SEARCH("Attention",I5)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Attention">
+      <formula>NOT(ISERROR(SEARCH("Attention",H19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
